--- a/쿼리분석/소스분석_요약_KS.xlsx
+++ b/쿼리분석/소스분석_요약_KS.xlsx
@@ -13,13 +13,14 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="소스분석_요약_KS" sheetId="1" r:id="rId4"/>
+    <x:sheet name="Sheet1" sheetId="2" r:id="rId5"/>
   </x:sheets>
   <x:calcPr xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" mc:Ignorable="hs" hs:hclCalcId="904"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
   <x:si>
     <x:t>제미나이 2단계 보완 사항이 적용된 암호화 칼럼 검증 소스</x:t>
   </x:si>
@@ -57,6 +58,12 @@
     <x:t>리니지 분석 결과물에 더해 암호화 대상 컬럼 매칭 결과물까지 한 번에 산출하여 다차원 통합 분석 기능 구현</x:t>
   </x:si>
   <x:si>
+    <x:t>| **12** | [sql_v12_full_new_03_local.py](file:///d:/workspace/enc/쿼리분석/sql_v12_full_new_03_local.py) | `&lt;분석대상_디렉토리&gt;`&lt;br&gt;`&lt;스키마.검색기준테이블&gt;`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;스키마.검색기준테이블&gt;`: 로컬 CSV 대신 검색 기준으로 사용하는 DB 내 테이블 | • `&lt;스키마.검색기준테이블&gt;`: 기준 정보가 담긴 DB 스키마/테이블 지정 (상시 DB 연동 동작) | 기준 정보를 로컬 CSV 대신 **DB 검색기준 테이블**에서 조회하여 동작하며, `tbl_name`과 `cols` (복합 칼럼 정보, 예: `col_01:k1,col_bb:k2`)를 파싱하여 개별 칼럼 단위 매칭을 수행합니다. 매칭이 없는 행도 NULL로 보존하는 예외처리가 추가되었습니다. |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **10** | [sql_v12_full_new.py](file:///d:/workspace/enc/쿼리분석/sql_v12_full_new.py) | `&lt;검색대상_디렉토리&gt;`&lt;br&gt;`&lt;경로포함_CSV파일명&gt;`&lt;br&gt;`[--mode &lt;SIMPLE/DETAIL&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;검색대상_디렉토리&gt;`: 소스 탐색 디렉토리&lt;br&gt;• `&lt;경로포함_CSV파일명&gt;`: table_name, column_name 헤더를 가진 기준 CSV 파일 경로 | • `&lt;경로포함_CSV파일명&gt;`: 매칭 검토 기준이 되는 CSV 경로 (동적으로 읽어 `in/` 폴더에 임시 저장) | `sql_v12_full_emrput.py`에 테이블/칼럼 매칭 기능을 결합하였습니다. 입력 CSV의 `table_name` 및 `column_name`과 일치하는 쿼리를 검색하여 칼럼매칭 결과 파일 및 DB 테이블(`{PROGRAM_NAME}_{last_dir}_{mode}_col_match`)을 생성합니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sql v12 full new 02 local.py</x:t>
   </x:si>
   <x:si>
@@ -81,6 +88,9 @@
     <x:t>외부 DB 조회 매칭을 접목한 통합 쿼리 분석 로컬 버전</x:t>
   </x:si>
   <x:si>
+    <x:t>| **11** | [sql_v12_full_new_02.py](file:///d:/workspace/enc/쿼리분석/sql_v12_full_new_02.py) | `&lt;검색대상_디렉토리&gt;`&lt;br&gt;`&lt;경로포함_CSV파일명&gt;`&lt;br&gt;`[--mode &lt;SIMPLE/DETAIL&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;경로포함_CSV파일명&gt;`: tbl_name, column_name, tobe_enc_key, tobe_enc_rsn 헤더를 가진 기준 CSV 파일 경로 | • `&lt;경로포함_CSV파일명&gt;`: 암호화 키 정보가 기재된 CSV 경로 | `sql_v12_full_new.py`에서 입력 CSV의 헤더명(`tbl_name`)을 변경하고, 결과 파일/테이블에 암호화 키 및 사유 정보(`tobe_enc_key`, `tobe_enc_rsn`)가 함께 적재 및 출력되도록 기능을 보완했습니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>CONF</x:t>
   </x:si>
   <x:si>
@@ -99,6 +109,9 @@
     <x:t>raw/clean 쿼리 분리 파싱, CSV 필드 레이아웃에서 query_text 제외 처리, exclude 테이블 별도 적재 모듈</x:t>
   </x:si>
   <x:si>
+    <x:t>| **7** | [sql_lng_015_emrput.py](file:///d:/workspace/enc/쿼리분석/sql_lng_015_emrput.py) | `&lt;소스디렉토리&gt;`&lt;br&gt;`[--mode &lt;SIMPLE/DETAIL&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;소스디렉토리&gt;`: SQL 리니지 분석 대상 디렉토리 경로&lt;br&gt;• `--mode`: 리니지 분석 모드 | • `--mode`: SIMPLE(기본, CTE 투명 처리) 또는 DETAIL(WITH절 CTE 임시테이블 흐름 포함) 중 선택 | 소스 코드로부터 테이블 간 데이터 흐름(Lineage)을 분석하여 CSV 및 DB에 저장하며, 추가적으로 파일 내에 **`EMRPUT`** 문자열이 포함된 라인을 감지하여 별도의 CSV 파일로 추출하는 기능이 탑재되어 있습니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>MySQL DB 커넥터 자동 로드, 테이블/뷰 정의 DML 쿼리 추출 로직, CTE(Common Table Expression) 리니지 분석 및 SIMPLE/DETAIL 모드 빌더, 테이블 적재 및 CSV 저장 모듈</x:t>
   </x:si>
   <x:si>
@@ -162,9 +175,21 @@
     <x:t>uld, ld, sh, sql, hql 확장자 파일 탐색기, 세미콜론(;) 단위 쿼리 스플리터, dat 형식 구분자 출력기</x:t>
   </x:si>
   <x:si>
+    <x:t>| **3** | [p190872_local_chk_v06_gm.py](file:///d:/workspace/enc/쿼리분석/p190872_local_chk_v06_gm.py) | `&lt;검색기준테이블&gt;`&lt;br&gt;`&lt;검색디렉토리&gt;`&lt;br&gt;`[--mid &lt;MID&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]`&lt;br&gt;`[--where &lt;old/new&gt;]`&lt;br&gt;`[--chk &lt;default/encdec_no&gt;]` | • `&lt;검색디렉토리&gt;`: 소스 탐색 로컬 경로&lt;br&gt;• `--mid`: 하위 MID 폴더 지정 (쉼표 구분)&lt;br&gt;• `--where`: 기준테이블 조회 조건 필터&lt;br&gt;• `--chk`: 암복호화 필터 적용 | • `--mid`: 미지정 시 전체 폴더 분석&lt;br&gt;• `--where`: 'old'/'new' 중 선택 필터&lt;br&gt;• `--chk`: 'default'(암복호화 포함) 또는 'encdec_no'(암복호화 제외) 중 선택 | 로컬 디렉토리 하위의 소스 파일들을 분석하여 칼럼 사용 여부를 상세 매칭합니다. 한 줄/블록 주석 내 매칭 제외, 순수 칼럼 참조 제외 필터(Omit/Include 룰)를 적용하여 가공이나 함수가 적용된 식만 추출하며, print.txt 및 제외행 exclude.txt 로그를 생성합니다. |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **1** | [p190872_local_chk_v04_gm.py](file:///d:/workspace/enc/쿼리분석/p190872_local_chk_v04_gm.py) | `&lt;스키마.검색기준테이블&gt;`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;스키마.검색기준테이블&gt;`: DB 내 검색 대상 기준 테이블 (필수)&lt;br&gt;• `--db`: DB 적재 활성화 여부 (선택)&lt;br&gt;• `--conf`: 설정 파일 경로 (선택) | • `--db`: 활성화 시 파싱 및 매칭 결과를 DB 테이블에 자동 적재&lt;br&gt;• `--conf`: `mysql.conf` 경로를 지정 | DB의 검색기준테이블을 조회하여 지정된 소스 파일(`source_file`)의 쿼리를 추출(주석 제거 포함)하고, `cols` 컬럼의 칼럼들이 소스 내에 매칭되는지 분석하여 cols 파싱, query_text, 매칭결과 3개의 CSV 생성 및 DB 적재를 처리합니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>default 분리 CSV 파일 내 암복호화 상태와 키의 매칭 상태를 검증하는 판정 로직을 완비하고 탐색 범위를 지정된 주요 확장자로만 좁혀 검출 효율성을 극대화함</x:t>
   </x:si>
   <x:si>
+    <x:t>### 분석 요약 표 (엑셀 파일과 동일한 내용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **4** | [p190872_local_chk_v08_gm.py](file:///d:/workspace/enc/쿼리분석/p190872_local_chk_v08_gm.py) | `&lt;검색기준테이블&gt;`&lt;br&gt;`&lt;검색디렉토리&gt;`&lt;br&gt;`&lt;검색결과테이블명&gt;`&lt;br&gt;`[--mid &lt;MID&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]`&lt;br&gt;`[--where &lt;old/new&gt;]`&lt;br&gt;`[--chk &lt;default/encdec_no/all&gt;]` | • `&lt;검색결과테이블명&gt;`: 결과 DB 테이블명 직접 지정&lt;br&gt;• `--chk`: 'all' 조건 추가&lt;br&gt;(기타 파라미터는 v06과 동일) | • `--chk`: 'all' 지정 시 default와 encdec_no의 분석 결과를 각각 분리 생성하여 적재 | v07_gm(주석 원본 유지, exclude 테이블 적재 등)을 계승하고 **암호화 파일 정상처리 여부 검증 로직**이 추가된 최종 버전입니다. 동일 라인 내 [컬럼명], [암복호화 함수], [tobe_enc_key 변환코드(e1~e4)]가 모두 있으면 "OK", 없으면 "NOT OK" 판정 후 검증 결과 CSV를 생성합니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>쿼리 리니지 추적기, 칼럼 매칭 판정 버퍼, MySQL DDL/INSERT 벌크 엔진</x:t>
   </x:si>
   <x:si>
@@ -180,6 +205,9 @@
     <x:t>사용자 요구사항인 암/복호화 키 포함/제외 필터를 추가하고 스키마 매핑 표준화 적용</x:t>
   </x:si>
   <x:si>
+    <x:t>* 대상 Python 소스 파일 12개의 코드를 읽어 매개변수 구조, 실행 예시, 변경 이력 및 내부 동작을 종합적으로 파싱 및 분석하였습니다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>분석 대상 소스 내 유효 SQL 쿼리 라인수를 추출하여 전체 소스 및 쿼리 규모 산정 데이터 생성</x:t>
   </x:si>
   <x:si>
@@ -201,6 +229,12 @@
     <x:t>p190872_local_chk_v05_gm_20260624.py</x:t>
   </x:si>
   <x:si>
+    <x:t>| **5** | [sql_est_010_load.py](file:///d:/workspace/enc/쿼리분석/sql_est_010_load.py) | `&lt;소스분석할 디렉토리경로&gt;`&lt;br&gt;`[--conf &lt;경로&gt;]` | • `&lt;소스분석할 디렉토리경로&gt;`: 소스 파일(.sh, .sql 등) 디렉토리 경로 | • `--conf`: DB 접속용 설정 파일 경로 지정 (미지정 시 자동 탐색) | 지정한 소스 디렉토리 내 파일들로부터 SQL 쿼리문들을 추출하여 out/ 폴더에 `.dat` 파일로 생성한 후, 이를 읽어 MySQL DB 테이블에 즉시 적재(Load) 처리합니다. |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **6** | [sql_est_010_load_line.py](file:///d:/workspace/enc/쿼리분석/sql_est_010_load_line.py) | `&lt;소스분석할 디렉토리경로&gt;`&lt;br&gt;`[--conf &lt;경로&gt;]` | (sql_est_010_load와 동일) | (sql_est_010_load와 동일) | `sql_est_010_load.py`와 기능이 동일하나, 분석의 정밀도를 위해 소스 파일 내 각 쿼리가 시작되는 **시작 라인 넘버(Line Number)**를 함께 추출하여 결과 파일(.dat) 및 DB 적재 테이블에 기록하도록 확장되었습니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>convert_key_to_code 키 변환기, 세 가지 케이스(Case 1/2/3) 판정 로직을 탑재한 verify_default_csv 검증기, allowed_exts 확장자 필터(uld, ld, sh, sql, hql)를 적용한 파일 탐색 엔진</x:t>
   </x:si>
   <x:si>
@@ -261,6 +295,9 @@
     <x:t>데이터베이스 기준 테이블 로더, 로컬 디렉토리 전용 파일 스캐너, SIMPLE/DETAIL 리니지 뷰어</x:t>
   </x:si>
   <x:si>
+    <x:t>| **8** | [sql_lng_015_with.py](file:///d:/workspace/enc/쿼리분석/sql_lng_015_with.py) | `&lt;소스디렉토리&gt;`&lt;br&gt;`[--mode &lt;SIMPLE/DETAIL&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | (sql_lng_015_emrput과 동일) | (sql_lng_015_emrput과 동일) | SQL 리니지 분석 및 DB/CSV 저장 도구로, 특히 `WITH` 절로 시작하는 CTE(Common Table Expression) 쿼리의 흐름을 파싱하는 데 특화되어 있으며, DETAIL 모드 실행 시 임시 테이블 흐름까지 상세 분석합니다. |</x:t>
+  </x:si>
+  <x:si>
     <x:t>소스 주제</x:t>
   </x:si>
   <x:si>
@@ -307,6 +344,30 @@
   </x:si>
   <x:si>
     <x:t>p190872_local_chk_v02_gm.py</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 분석된 상세 정보를 토대로 전문적인 엑셀 스타일링 서식이 적용된 생성 스크립트 [generate_excel.py](file:///d:/workspace/enc/쿼리분석/generate_excel.py)를 작성하여 저장하였습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>* 터미널 환경에서 실행 가능한 명령어를 안내드렸으며, 마크다운 표로도 가독성 있게 정리하였습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>---</x:t>
+  </x:si>
+  <x:si>
+    <x:t>**작업 요약:**</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| No | 프로그램명 | 파라미터 | 파라미터 내용 | 옵션 설명 | 주요 기능 |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| :---: | :--- | :--- | :--- | :--- | :--- |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **2** | [p190872_local_chk_v05_gm.py](file:///d:/workspace/enc/쿼리분석/p190872_local_chk_v05_gm.py) | `&lt;스키마.검색기준테이블&gt;`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | (v04와 동일) | (v04와 동일) | v04_gm 버전에서 매칭 정확도를 강화하기 위해, 기존의 단순 포함(in 연산) 방식을 **정규식 단어 완전일치(`\b단어\b`)** 매칭 방식으로 수정하고, 생성되는 DB 테이블명에 프로그램명과 구분자(`_v05`)가 포함되도록 보완했습니다. |</x:t>
+  </x:si>
+  <x:si>
+    <x:t>| **9** | [sql_v12_full_emrput.py](file:///d:/workspace/enc/쿼리분석/sql_v12_full_emrput.py) | `&lt;소스디렉토리&gt;`&lt;br&gt;`[--mode &lt;SIMPLE/DETAIL&gt;]`&lt;br&gt;`[--db]`&lt;br&gt;`[--conf &lt;경로&gt;]` | (sql_lng_015_emrput과 동일) | (sql_lng_015_emrput과 동일) | 리니지 분석 기능과 함께, 실제 분석된 쿼리의 원본 텍스트를 담은 별도의 **쿼리 텍스트 테이블**(`{리니지테이블명}_query_text`)을 자동으로 생성하고 적재(TRUNCATE 후 INSERT)하는 기능이 통합된 완성 버전입니다. |</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1088,7 +1149,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -1099,9 +1160,6 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1828,7 +1886,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:I29"/>
+  <x:dimension ref="A1:I36"/>
   <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="38.125" style="1" bestFit="1" customWidth="1"/>
@@ -1839,122 +1897,122 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C1" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>89</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B5" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B6" s="2" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
         <x:v>7</x:v>
@@ -1965,27 +2023,27 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
         <x:v>8</x:v>
@@ -1993,27 +2051,27 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
         <x:v>9</x:v>
@@ -2021,83 +2079,83 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B14" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B16" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B18" s="2" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B18" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
         <x:v>10</x:v>
@@ -2105,13 +2163,13 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B20" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
         <x:v>11</x:v>
@@ -2119,124 +2177,280 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
-      <x:c r="A25"/>
-      <x:c r="B25"/>
+      <x:c r="A25" s="2" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B25" s="2" t="s">
+        <x:v>94</x:v>
+      </x:c>
       <x:c r="C25"/>
       <x:c r="D25"/>
     </x:row>
     <x:row r="26" spans="1:9" customFormat="1">
       <x:c r="A26" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B26" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H26" s="2"/>
       <x:c r="I26" s="2"/>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C27" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H27" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I27" s="2"/>
     </x:row>
     <x:row r="28" spans="1:9" customFormat="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F28" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G28" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H28" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I28" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:1" customFormat="1">
+      <x:c r="A29" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:1">
+      <x:c r="A30" s="2" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:1">
+      <x:c r="A31" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:1">
+      <x:c r="A32" s="2" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:1">
+      <x:c r="A33" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:1">
+      <x:c r="A34" s="2" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:1">
+      <x:c r="A35" s="2" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="G28" s="2" t="s">
+    </x:row>
+    <x:row r="36" spans="1:1">
+      <x:c r="A36" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="H28" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="I28" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:1" customFormat="1">
-      <x:c r="A29" s="4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr codeName="Sheet2"/>
+  <x:dimension ref="A1:A22"/>
+  <x:sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.399999999999999"/>
+  <x:cols>
+    <x:col min="1" max="6" width="61.625" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:1">
+      <x:c r="A1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:1">
+      <x:c r="A3" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:1">
+      <x:c r="A4" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:1">
+      <x:c r="A5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:1">
+      <x:c r="A9" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:1">
+      <x:c r="A10" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:1">
+      <x:c r="A11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:1">
+      <x:c r="A12" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:1">
+      <x:c r="A13" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:1">
+      <x:c r="A14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:1">
+      <x:c r="A15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:1">
+      <x:c r="A16" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:1">
+      <x:c r="A18" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:1">
+      <x:c r="A19" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:1">
+      <x:c r="A20" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:1">
+      <x:c r="A21" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:1">
+      <x:c r="A22" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.74805557727813721" right="0.74805557727813721" top="0.98430556058883667" bottom="0.98430556058883667" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
+</x:worksheet>
 </file>